--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N56_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N56_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>16.27295166949282</v>
+        <v>2.644354646292584</v>
       </c>
       <c r="D2" t="n">
-        <v>41.69850225588544</v>
+        <v>6.776006616581384</v>
       </c>
       <c r="E2" t="n">
-        <v>18.05619908458315</v>
+        <v>2.934132351244762</v>
       </c>
       <c r="F2" t="n">
-        <v>9.619850095554105</v>
+        <v>1.563225640527542</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>31.32486525494211</v>
+        <v>5.090290603928094</v>
       </c>
       <c r="D3" t="n">
-        <v>31.79185215907065</v>
+        <v>5.166175975848981</v>
       </c>
       <c r="E3" t="n">
-        <v>18.05619908458315</v>
+        <v>2.934132351244762</v>
       </c>
       <c r="F3" t="n">
-        <v>9.619850095554105</v>
+        <v>1.563225640527542</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.03388780409803</v>
+        <v>4.23050676816593</v>
       </c>
       <c r="D4" t="n">
-        <v>18.24669752718463</v>
+        <v>2.965088348167502</v>
       </c>
       <c r="E4" t="n">
-        <v>18.05619908458315</v>
+        <v>2.934132351244762</v>
       </c>
       <c r="F4" t="n">
-        <v>9.619850095554105</v>
+        <v>1.563225640527542</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.09456148674582</v>
+        <v>5.377866241596196</v>
       </c>
       <c r="D5" t="n">
-        <v>14.56994689615268</v>
+        <v>2.367616370624811</v>
       </c>
       <c r="E5" t="n">
-        <v>18.05619908458315</v>
+        <v>2.934132351244762</v>
       </c>
       <c r="F5" t="n">
-        <v>9.619850095554105</v>
+        <v>1.563225640527542</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.21309050516326</v>
+        <v>6.69712720708903</v>
       </c>
       <c r="D6" t="n">
-        <v>18.58762762334667</v>
+        <v>3.020489488793833</v>
       </c>
       <c r="E6" t="n">
-        <v>18.05619908458315</v>
+        <v>2.934132351244762</v>
       </c>
       <c r="F6" t="n">
-        <v>9.619850095554105</v>
+        <v>1.563225640527542</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>56.0357029044876</v>
+        <v>9.105801721979235</v>
       </c>
       <c r="D7" t="n">
-        <v>12.73593671838765</v>
+        <v>2.069589716737994</v>
       </c>
       <c r="E7" t="n">
-        <v>18.05619908458315</v>
+        <v>2.934132351244762</v>
       </c>
       <c r="F7" t="n">
-        <v>9.619850095554105</v>
+        <v>1.563225640527542</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>45.55977343539782</v>
+        <v>7.403463183252145</v>
       </c>
       <c r="D8" t="n">
-        <v>7.733778788420016</v>
+        <v>1.256739053118253</v>
       </c>
       <c r="E8" t="n">
-        <v>18.05619908458315</v>
+        <v>2.934132351244762</v>
       </c>
       <c r="F8" t="n">
-        <v>9.619850095554105</v>
+        <v>1.563225640527542</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>51.54609587543949</v>
+        <v>8.376240579758917</v>
       </c>
       <c r="D9" t="n">
-        <v>14.12868253721292</v>
+        <v>2.295910912297099</v>
       </c>
       <c r="E9" t="n">
-        <v>18.05619908458315</v>
+        <v>2.934132351244762</v>
       </c>
       <c r="F9" t="n">
-        <v>9.619850095554105</v>
+        <v>1.563225640527542</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>57.17045674404653</v>
+        <v>9.290199220907562</v>
       </c>
       <c r="D10" t="n">
-        <v>15.25052745770723</v>
+        <v>2.478210711877425</v>
       </c>
       <c r="E10" t="n">
-        <v>18.05619908458315</v>
+        <v>2.934132351244762</v>
       </c>
       <c r="F10" t="n">
-        <v>9.619850095554105</v>
+        <v>1.563225640527542</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>58.13776741499453</v>
+        <v>9.447387204936613</v>
       </c>
       <c r="D11" t="n">
-        <v>4.042809409124374</v>
+        <v>0.6569565289827107</v>
       </c>
       <c r="E11" t="n">
-        <v>18.05619908458315</v>
+        <v>2.934132351244762</v>
       </c>
       <c r="F11" t="n">
-        <v>9.619850095554105</v>
+        <v>1.563225640527542</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>63.09240283859796</v>
+        <v>10.25251546127217</v>
       </c>
       <c r="D12" t="n">
-        <v>5.772957147580972</v>
+        <v>0.938105536481908</v>
       </c>
       <c r="E12" t="n">
-        <v>18.05619908458315</v>
+        <v>2.934132351244762</v>
       </c>
       <c r="F12" t="n">
-        <v>9.619850095554105</v>
+        <v>1.563225640527542</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>65.5</v>
+        <v>10.64375</v>
       </c>
       <c r="D13" t="n">
-        <v>12.84214674418114</v>
+        <v>2.086848845929435</v>
       </c>
       <c r="E13" t="n">
-        <v>18.05619908458315</v>
+        <v>2.934132351244762</v>
       </c>
       <c r="F13" t="n">
-        <v>9.619850095554105</v>
+        <v>1.563225640527542</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>68.01451440924606</v>
+        <v>11.05235859150249</v>
       </c>
       <c r="D14" t="n">
-        <v>6.204360278715177</v>
+        <v>1.008208545291216</v>
       </c>
       <c r="E14" t="n">
-        <v>18.05619908458315</v>
+        <v>2.934132351244762</v>
       </c>
       <c r="F14" t="n">
-        <v>9.619850095554105</v>
+        <v>1.563225640527542</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>73.66987172514962</v>
+        <v>11.97135415533681</v>
       </c>
       <c r="D15" t="n">
-        <v>20.45358903536623</v>
+        <v>3.323708218247012</v>
       </c>
       <c r="E15" t="n">
-        <v>18.05619908458315</v>
+        <v>2.934132351244762</v>
       </c>
       <c r="F15" t="n">
-        <v>9.619850095554105</v>
+        <v>1.563225640527542</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>81.891696770796</v>
+        <v>13.30740072525435</v>
       </c>
       <c r="D16" t="n">
-        <v>18.96160810001561</v>
+        <v>3.081261316252538</v>
       </c>
       <c r="E16" t="n">
-        <v>18.05619908458315</v>
+        <v>2.934132351244762</v>
       </c>
       <c r="F16" t="n">
-        <v>9.619850095554105</v>
+        <v>1.563225640527542</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
